--- a/survey_templates/035_environmental_sustainability_in_hospitals_survey--survey_templates.xlsx
+++ b/survey_templates/035_environmental_sustainability_in_hospitals_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,19 +520,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>intro1</t>
+          <t>intro_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Environmental Sustainability In Hospitals</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -552,41 +548,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>facility_type</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Facility Type</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>facility_type_2</t>
+          <t>green_initiatives_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>environmental_sustainability_in_hospitals_survey</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Green Initiatives</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -596,67 +584,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>facility_type_3</t>
+          <t>challenges_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hospital_facility_type</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>green_initiatives_1</t>
+          <t>ideas_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>green_initiatives</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Ideas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>green_initiatives_2</t>
+          <t>questions_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>green_initiatives_in_hospitals</t>
+          <t>Questions</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -669,44 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>challenges_1</t>
+          <t>questions_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>challenges</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Questions (Text Field)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>challenges_2</t>
+          <t>questions_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hospitals_challenges</t>
+          <t>Date of Data Collection</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -719,27 +699,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ideas_1</t>
+          <t>questions_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ideas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Time of Data Collection</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -751,62 +727,58 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ideas_2</t>
+          <t>questions_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ideas_to_improve</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>questions_1</t>
+          <t>questions_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Additional Questions</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>questions_2</t>
+          <t>questions_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>hospitals_questions</t>
+          <t>Environmental Performance</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -819,50 +791,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>questions_3</t>
+          <t>questions_8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>environmental_performance</t>
+          <t>Questions Asked</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>questions_4</t>
+          <t>questions_9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>questions_to_improve</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>Questions 9</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -874,41 +842,41 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>questions_5</t>
+          <t>questions_10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>questions</t>
+          <t>Questions Asked In</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>questions_6</t>
+          <t>questions_11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>questions_to_ask</t>
+          <t>Questions To Answer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -920,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>questions_7</t>
+          <t>questions_12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hospitals_questions</t>
+          <t>Questions 12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -938,184 +906,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>questions_8</t>
+          <t>questions_13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>questionnaire</t>
+          <t>Questions In Hospitals</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>questions_9</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>questions_asked</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>questions_10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>questions_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>questions_asked_in</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>questions_12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>questions_to_answer</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>questions_13</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>questions_14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>questions_in_hospitals</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>questions_15</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>questions</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1130,11 +937,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1163,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1180,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1197,46 +1004,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facility_type_3_choices</t>
+          <t>green_initiatives_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>facility_type_3_choices</t>
+          <t>green_initiatives_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1248,46 +1055,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>green_initiatives_1_choices</t>
+          <t>challenges_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>green_initiatives_1_choices</t>
+          <t>challenges_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1299,46 +1106,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>challenges_1_choices</t>
+          <t>questions_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>challenges_1_choices</t>
+          <t>questions_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1350,46 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>questions_1_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>questions_1_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
